--- a/docs/HOR Abonēšnas cenas.xlsx
+++ b/docs/HOR Abonēšnas cenas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raivis.Biskaps\Documents\Claude\Projects\Horizon pārdošana\docs-qa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF30126-E7A9-47DF-8740-2BAB8DD81171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E11093-4BF4-493A-BBF6-E37E65874F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,10 +65,10 @@
     <t>BIZNESS</t>
   </si>
   <si>
-    <t>Abonēšanas papildiespējas</t>
-  </si>
-  <si>
     <t>Abonēšanas cena mēnesī (EUR bez PVN)</t>
+  </si>
+  <si>
+    <t>Horizon abonēšanas pozīcijas</t>
   </si>
 </sst>
 </file>
@@ -392,10 +392,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/docs/HOR Abonēšnas cenas.xlsx
+++ b/docs/HOR Abonēšnas cenas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raivis.Biskaps\Documents\Claude\Projects\Horizon pārdošana\docs-qa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E11093-4BF4-493A-BBF6-E37E65874F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042A2873-8C0E-4A4B-B6FB-7D2C5D4ABBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>PAMATS (2 Horizon lietotājiem, 20 darbiniekiem)</t>
   </si>
@@ -69,6 +69,78 @@
   </si>
   <si>
     <t>Horizon abonēšanas pozīcijas</t>
+  </si>
+  <si>
+    <t>Iekļautie moduļi, funkcionalitātes</t>
+  </si>
+  <si>
+    <t>- Grāmatvedība  
+- Noliktava  
+- Darba samaksa (algas) un Perosnāla uzskaite  
+- HoP algas lapiņas  
+- Banka  
+- Dokumentu imports un eksports  
+- Vairāki nodokļu maksātāji vienā datu apgabalā  
+- Vairākas nodalītas firmas  
+- Atskaišu redaktors  
+- Tiesības un lomas  
+- Brīdinājumi  
+- Daudzvalodu režīms (LV, EE, LT, ENG)  
+- Failu glabātuves  
+- Automātiskie darbi  
+- MS Excel spraudnis  
+- Lietotāju pārvaldība  
+- Virsgrāmata  
+- Finanšu pārskati  
+- E-rēķinu aprite  
+- Apgāde un realizācija  
+- Kase un banka  
+- Nākamie periodi  
+- Avansa norēķini  
+- Pamatlīdzekļi  
+- Budžeta kontrole  
+- Līgumu uzskaite  
+- Integrācija ar kases aparātiem  
+- Noliktavas uzskaite  
+- Preču kustība.  
+- Preču apgrozījuma un atlikumu pārskati.  
+- Elastīgi pārdošanas cenu un atlaižu mehānismi.  
+- Iepirkumu pārvaldība \- pasūtāmā krājumu daudzuma aprēķins.  
+- Sasaiste ar svītrkodu skeneriem.  
+- Realizācijas pārskati dažādos griezumos.  
+- Datu imports no MS Excel un cita formāta failiem.  
+- Integrācija ar kases sistēmām.</t>
+  </si>
+  <si>
+    <t>- HoP rēķinu saskaņošana  
+- Elektroniskā inventarizācija (pamatlīdzekļi, inventārs)  
+- Maksājumu automatizācija (gateway)  
+- Inventārs  
+- HoP pamatlīdzekļi un inventārs (materiālie resursi)  
+- Autotransports  
+- Debitoru novērtēšana  
+- Pakalpojumu līgumu uzskaite  
+- Iepirkumu līgumu kontrole  
+- HoP atskaites</t>
+  </si>
+  <si>
+    <t>- Darbinieku pašapkalpošanās \- HoP personāls  
+- HoP pieteikumi  
+- HoP rīkojumi un vienošanās  
+- HoP esmu iepazinies \- noteikumi, inzstrukcijas  
+- HoP komandējumi  
+- HoP mani izdevumi, saimnieciskie avansi, čeki digitalizēšana ar MI  
+- HoP darba laika uzskaite  
+- Elektroniska dokumentu saskaņošana  
+- Drošs elektroniskais paraksts  
+- HoP atskaites</t>
+  </si>
+  <si>
+    <t>- Loģistika (Vairumtirdzniecība, piegāžu pārvaldība)  
+- Ražošana  
+- HPos, Strongpoint kases sistēma, Mazumtirdzniecība  
+- Apsaimniekošana, NĪP, Nekustamie īpašumi  
+- Integrācijas platforma</t>
   </si>
 </sst>
 </file>
@@ -155,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -165,6 +237,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,30 +458,37 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.77734375" customWidth="1"/>
     <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
         <v>74</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -414,7 +496,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -422,7 +504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -430,7 +512,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -438,15 +520,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="171.6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="4">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>1</v>
       </c>
@@ -454,7 +539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -462,15 +547,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="198" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="4">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -478,7 +566,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -486,16 +574,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="4">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/HOR Abonēšnas cenas.xlsx
+++ b/docs/HOR Abonēšnas cenas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raivis.Biskaps\Documents\Claude\Projects\Horizon pārdošana\docs-qa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042A2873-8C0E-4A4B-B6FB-7D2C5D4ABBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132F082E-1618-4F63-B686-2EBD714E8EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>PAMATS (2 Horizon lietotājiem, 20 darbiniekiem)</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Papildu 1 Horizon lietotājs (no 11. lietotāja)</t>
-  </si>
-  <si>
-    <t>GRĀMATVEDĪBA PLUS (20 darbiniekiem)</t>
   </si>
   <si>
     <t>PERSONĀLS (20 HoP lietotāji)</t>
@@ -141,6 +138,21 @@
 - HPos, Strongpoint kases sistēma, Mazumtirdzniecība  
 - Apsaimniekošana, NĪP, Nekustamie īpašumi  
 - Integrācijas platforma</t>
+  </si>
+  <si>
+    <t>Pamatsistēma</t>
+  </si>
+  <si>
+    <t>Horizon struktūras daļa</t>
+  </si>
+  <si>
+    <t>GRĀMATVEDĪBA + (20 darbiniekiem)</t>
+  </si>
+  <si>
+    <t>GRĀMATVEDĪBA +</t>
+  </si>
+  <si>
+    <t>PERSONĀLS</t>
   </si>
 </sst>
 </file>
@@ -458,135 +470,175 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="62.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
-    <col min="3" max="3" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.88671875" customWidth="1"/>
+    <col min="2" max="2" width="62.77734375" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="4" max="4" width="39.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>74</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="409.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4">
-        <v>74</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="3" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="158.4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="8" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="C8" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="171.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C9" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="4">
+    </row>
+    <row r="10" spans="1:4" ht="171.6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4">
         <v>25</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="4">
+    <row r="11" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="198" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4">
-        <v>25</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="C12" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="92.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4">
+        <v>46</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="105.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4">
-        <v>46</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
